--- a/data/scans.xlsx
+++ b/data/scans.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N275"/>
+  <dimension ref="A1:N311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20562,16 +20562,2812 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>100000107341927070</t>
-        </is>
+      <c r="M275" t="n">
+        <v>1.000001073419271e+17</v>
       </c>
       <c r="N275" t="inlineStr">
         <is>
           <t>IBD3419270707</t>
         </is>
       </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-03-14 01:45:28</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>KEMCO80SS104KSRA</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>5.81s</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO80SS104KSRA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY 2SOO
+.100UF 50V
+10%
+DATE CODE :2S42
+:
+C OF O MEXICO
+1T LOT:254270641
+S0L456
+45239701
+KEMET
+KEMET P/N CO8OSS104KSRAC7800
+MIL P/N
+8 YAGEO COMPANY
+L</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>df0a4361563cc39f80107d6c0b6b71df336dd7b9388aa25a6c99018e28d45372</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
+        <v>1.000001073452728e+17</v>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-03-14 01:46:45</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>012685</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>3.66s</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>JAUCH
+O
+1P 253468
+(0) 1000 ST
+PB
+V
+D
+(1) 012685
+ROHS
+−
+MINOONY
+Q 8,0 -JXS53P4 -10 -20/20 -T1-AEC-LF
+OHEPT!G6 -85
+(0)</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>a72766a5857d9bad311adf615c3f8a8d2b7b8903aec0164f963706bee856c761</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>1.000001073452806e+17</v>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:00:20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>KEMC0805S104KSRA</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>3.99s</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO805S104KSRA
+Q QUANTITY 2SOO
+CAPACITOR
+ROHS-PRC
+−
+.100UF SOV
+10%
+DATE CODE :2542
+1T LOT:254270641
+C OF O MEXICO
+S
+45239701
+KEMET P/N C080SS104K5RAC7800
+KEMET
+MIL P/N
+YADEO CN
+B
+1</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>8cd8048130d4dc6e178fb4d69e4869c36c99f8eea54e901cf94cb8f37d2af1ee</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:01:24</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>3.64s</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>JAUCH
+99
+1P 253468
+(B
+(0) 1000 ST
+-
+O
+(11) 012685
+ROHS
+JEILBVTY
+0 8,0 -JXS53P4 - 10 -20/20 -T1-AEC-LF
+6MEP10236-85
+2</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>fea38d2b473ea547695d9026cee691bdfcba3509c536e3bba84d630aa87d3355</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:02:19</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>012685</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>3.35s</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>JAUCH
+1P 253468
+−
+-
+_
+(0) 1000 ST
+/
+ROHS
+D
+1T 012685
+JOISWVLY
+0 8,0 -JXS53P4 - 10-20/20-T1-AEC-LF
+OHEPIG6 -5
+.
+=
+1</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>80b38eb070350314799559b8f3934b38cade7a03b33fbf18cce70aa187d1011c</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:02:45</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>KEMC0805S104K5RA</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>3.40s</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO805S104K5RA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY2500
+.100UF SOV
+10%
+DATE CODE :2542
+(IT) LOT:254270641
+C OF O MEXICO
+45239701
+KEMET
+KEMET P/N CO8OSS104KSRAC7800
+MIL P/N
+U</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>eef8b70918e3b83e71a4d29d017aff72bf39ba3c0b80e70d995232d33c227a41</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:03:00</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>3.79s</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO8OSS104KSRA
+¤
+CAPACITOR
+ROHS-PRC
+Q QUANTITY2500
+.100UF S0V
+10%
+DATE CODE :2542
+1T LOT:254270641
+COF O MEXICO
+1
+45239701
+KEMET
+KEMET P/N COBOSS104KSRAC7800
+MIL P/N
+YAGEO
+O
+2
+:</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>ef7e091d2f88fe54bc6da2ef126d95222e9f125c6b978c681ba1122f163d9765</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:03:59</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>3.08s</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>JAUCH
+Q9
+1P 253468
+(0) 1000 ST
+1T 012685
+ROHS
+052
+JOILMVY
+Q 8,0-JXS53P4 -10 -20/20-T1-AEC-LF
+ONEPIUG6-85
+0
+{
+D</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>9191cba3fe9aee98952bf5816f0d4545598405aa1007fce2888ddcdd7221b78c</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:07:12</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>2.74s</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>U
+D
+0
+8
+M
+3$</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>e868fc5b79834840e1c3a2441a0fbf9eba0bd02828283ee2d7b9cc0dcf893913</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:07:31</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>WOLYNALEDES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2.94s</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>0
+67
+WOLYNALEDES
+TTTQIHYY.
+N.&lt;-
+, •
+Y</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>d701d663e34b27dec217e73b8c23fbdd606b7266773265985739fc4ef7094d8d</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:07:35</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>3.10s</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>0
+." 'S
+1
+(VAKD
+G
+I~
+-
+2</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>90ded1b745df423ae380f8a07694c1861c1c0f57c31688ab8194fc7d33475632</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:27:33</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2.36s</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>0f245680138b336171220cce50f537e20e6f6cc6424ac37218cbc8e08de2cfcc</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:27:55</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>3.40s</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>JAUCH
+1P 253468
+(0) 1000 ST
+PB
+1T 012685
+ROHS
+"
+JOINY
+U
+2
+Q 8,0 -JXS53P4 -10 -20/20-T1-AEC-LF
+OHEPI0156-85
+O
+U</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>1a9356d6fffc188694a7048a40c68179d5924ffbb058dab88396e5ad3edc63a0</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:29:06</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>KEMCOBOSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>4.07s</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCOBOSS104KSRA
+1
+CAPACITOR
+ROHS-PRC
+Q QUANTITY2500
+.100UF S0V
+10%
+..--
+DATE CODE :2542
+C OF O MEXICO
+1T LOT:254270641
+50:436
+$45239701
+KEMET
+KEMET P/N C080SS104KSRAC7800
+MIL P/N
+WY
+—
+0
+(</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>6fce36d94dfa0a6f5314b0a15282722043b55735eddea9a673908236a34e2868</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:32:56</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>2.63s</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>984edcecc5ebcb27076919e1eda72640e8a8877e6f9337500c74b9102def4bc0</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:33:26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>KEMC0805S104K5RA</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>4.79s</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>7
+P PART NUMBER:KEMCO805S104K5RA
+?
+ED
+CAPACITOR
+ROHS-PRC
+Q QUANTITY2500
+10%
+.100UF SOV
+DATE CODE :2542
+COF O MEXICO
+1T LOT:254270641
+11
+E
+01
+45239701
+KEMET
+KEMET P/N COBOSS104KSRAC7800
+MIL P/N
+A YAGEO CARPORY
+!</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>0fbc93a3b306b009bc97e3d2e663979befc033084b3b70fa78fd2907f977b743</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:34:14</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>3.20s</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>U
+0
+6
+2
+A</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>a72e584f7eaec99ead66cad44fe2b2cc5f31ea6991808a00349f4279a7da1ad9</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:34:29</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>5.05s</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO8OSS104KSRA
+"•AMY
+Q QUANTITY 2SOO
+CAPACITOR
+ROHS-PRC
+.100UF 50V
+10%
+DATE CODE :2S42
+2
+1T LOT:254270641
+C OF O MEXICO
+TE
+59:496
+45239701
+KEMET P/N CO8OSS104KSRAC7800
+KEMET
+MIL P/N
+A YAGEO CY
+~
+$\RA }$</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>a6d0b2d2ced15781fab8afe27704e967d2292cf782a47a92190a4219c9e9de89</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:35:02</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>4.03s</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>(
+JAUCH
+0.9
+1P 253468
+() 1000 ST
+_
+ROHS
+(11) 012685
+OLLBEVLY
+Q 8,0 -JXS53P4 -10 -20/20 -T1-AEC-LF
+OMEPL036-85
+!</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>57b1e367fb4df9ac45b350f0136f42d2a740571aa0b51af587239996899f2b59</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:36:06</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>3.89s</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>3
+P PART NUMBER:KEMCO8OSS104KSRA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY 2500
+.100UF 50V
+10%
+DATE CODE :2542
+:
+,00
+C OF O MEXICO
+1T LOT:254270641
+45239/01
+KEMET
+KEMET P/N CO80SS104KSRAC7800
+MIL P/N
+A YAGEO CY
+0
+!</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>23c0890915aa9e9af77dfba70f6c642632002680ca637ab44abd541f94963aad</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:37:05</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>3.86s</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>1
+(:
+JAUCH
+00
+1P 253468
+() 1000 ST
+B
+(17) 012685
+ROHS
+PAM2Y
+120
+0 8,0 -JXS53P4 -10-20/20-T1-AEC-LF
+OHEPRUG6-8S
+7Y
+A
+J
+45</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>20da2494ae7d6b3803ca10190f546b0b1f91b3a0afa7bb508ce72b6061634553</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:37:18</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>3.73s</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>JAUCH
+0.0
+1P 253468
+(0) 1000 ST
+0
+(1) 012685
+ROHS
+NWMY!
+Q 8,0 -JXS53P4 -10 -20/20 -T1-AEC-LF
+C
+57
+6NEPLUG6-85
+*</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>07cf285e512a37dc86161a9bfdbba2d0693d52d7b0429a342ef6371836d911e1</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:38:57</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>2.84s</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>U
+A
+0
+−
+4
+07</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>35276e51383713cbb32c9e1a78d0552ec5ac9825bb5211de45bebd1914c85d24</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:39:06</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>3.42s</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>JAUCH
+1P 253468
+(0) 1000 ST
+O
+(11) 012685
+ROHS
+IWYT
+00
+0 8,0-JXS53P4-10 -20/20-T1-AEC-LF
+ONEPI0136-85
+F
+7
+U</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>d1f3c4e16d25ecddc544b6dea88ccc13405c322fc0ba0c1dfb2d7908984ba149</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:39:40</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>KEMCOBO5S104KSRA</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>4.19s</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>B
+P PART NUMBER:KEMCOBO5S104KSRA
+Q QUANTITY2SOO CAPACITOR
+ROHS-PRC
+AEE
+.100UF 50V
+10%
+DATE CODE :2S42
+FG
+C OF O MEXICO
+1T LOT :254270641
+1
+45239701
+KEMET
+M
+KEMET P/N CO80SS104KSRAC7800
+MIL P/N</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>7bbf74085bc5734ce8f814c15586fecc32e1cf89287718ae0e5716b298a26bd3</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:45:27</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>KEMC0805S104KSRA</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>4.65s</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>I!
+(
+P PART NUMBER:KEMCO805S104KSRA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY 2500
+.100UF 50V
+10%
+DATE CODE :2542
+C OF O MEXICO
+1T LOT:254270641
+COE
+=
+5PL46
+#45239701
+KEMET
+KEMET P/N CO8OSS104KSRAC7800
+MIL P/N
+1
+YAGEO E
+ME
+R</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>4400d87008199ce3c61dca15ea28352d0c1bb1870ad2c6ec874bc22d1908514a</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:45:49</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>3.69s</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>(
+AUCH
+Q
+1P 253468
+6
+() 1000 ST
+OO
+1T 012685
+ROHS
+PILNVIY
+D
+0 8,0 -JXS53P4 - 10 -20/20-T1 -AEC-LF
+M
+ONEPIUG6-S
+1
+0
+7</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>d7507944d75de3ad01baa295610a54e7d60ee98360a3ca46ca36c63f8e5cb113</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:46:04</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>3.92s</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>(
+AUCH
+000
+1P 253468
+Q 1000 ST
+(PB
+O
+1T 012685
+ROHS
+PILNVIY
+.
+Q 8,0-JXS53P4-10-20/20-T1-AEC-LF
+OHEPTU136-85
+F
+{
+3</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>9bc1a93bd9907b16c039d98e70c901187c295cc26f58b56879527fc0b47c63bd</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:46:14</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>3.73s</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>JAUCH
+1P 253468
+7
+(0) 1000 ST
+AB
+5
+O
+%
+(1) 012685
+_
+ROHS
+YOISNVR
+U
+2
+Q 8,0 -JXS53P4 -10-20/20-T1-AEC-LF
+1
+OHEPT06-85
+11</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>bb2bf6a68034e454b20ce0288ba68ba80a4c70278511e3b0d3f14302404c6490</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:46:39</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>3.21s</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>0
+F
+C
+31</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>92ae8e5174e096e5538437893cefd407521211ca12e9a7ba85973013bac21914</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:46:49</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>4.05s</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>JAUCH
+0E
+1P 253468
+P
+(0) 1000 ST
+ROHS
+(17) 012685
+3.
+OLVY
+2
+Q 8,0 -JXS53P4 -10 -20/20 -T1-AEC-LF
+OMEPT926-85
+—
+1;</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>1e1ba879b175f951c1a87d3b135672871a47855345f92219768bd33d5929f354</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:47:18</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>KEMC0805S104K5RA</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>5.06s</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO805S104K5RA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY 2S00
+.100UF 50V
+10%
+DATE CODE :2S42
+1
+COF O MEXICO
+1T LOT:254270641
+3CL486
+45239701
+KEMET
+KEMET P/N CO8OSS104K5RAC7800
+MIL P/N
+A YAGCO
+G
+(0)
+/
+}
+R</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>373e350e72e35d33df14c144f77812aebbc4ac0f74991193cadf46c5fd51e4b7</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:47:34</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>KEMC0805S104KSRA</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>4.08s</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO805S104KSRA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY2500
+.100UF 50V
+10%
+DATE CODE :2542
+1T LOT:254270641
+C OF O MEXICO
+∵
+U
+SFL486
+5
+45239701
+KEMET P/N C080SS104KSRAC7800
+KEMET
+MIL P/N
+A YAGCO CO
+T
+3</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>243388d36135c22fa0664f2315902bcac9a6f00ba4203eb21caf761b36e8d67e</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M308" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:47:58</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>4.75s</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO8OSS104KSRA
+ROHS-PRC
+CAPACITOR
+Q QUANTITY2500
+.100UF S0V
+10%
+.
+DATE CODE :2542
+C OF O MEXICO
+1T LOT:254270641
+62
+$*456
+45239701
+-
+KEMET
+KEMET P/N C08OSS104KSRAC7800
+MIL P/N
+A YAGEO CO
+B</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>5593f26c55771fbc92d4fc9a94277fa98ea6e30dded9083f7eab7da9f3ca4549</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M309" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:48:24</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>4.52s</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>JAUCH
+1P 253468
+L
+Q 1000 ST
+P
+(1) 012685
+ROHS
+-
+U
+OIUNVTY
+5
+Q 8,0-JXS53P4-10-20/20 -T1-AEC-LF
+ONEPTUG6-85
+M
+3
+(
+2
+:</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>6c45f086c0761c352e9c878137d92c7b304e870ad22334dc1d97622c0016174c</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-03-14 02:48:45</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>2.38s</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>3dd3f725924eb39aa526ef497f70edecc2c107928cb1c38d7d67b9071434cd8e</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/scans.xlsx
+++ b/data/scans.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N311"/>
+  <dimension ref="A1:N314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23369,6 +23369,263 @@
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr"/>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-03-14 06:32:57</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>NUM8ER</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>7.82s</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>P
+P PART NUM8ER:KEMCO805S104KSRA
+'
+Q QUANTITY2S00
+CAPACITOR
+ROHS-PRC
+T
+−
+.100UF 50V
+10%
+DATE CODE :2542
+1T LOT:254270641
+C OF O MEXICO
+046
+45239701
+KEMET P/N CO8OSS104KSRAC7800
+KEMET
+MIL P/N
+A YAGEO COMPONY
+C
+7</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>53de29547c962802e57a5cb16ec745c5b3811a4d7480e23f38dfacbdb088a002</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M312" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-03-14 06:33:45</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>7.57s</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>U
+4
+P PART NUMBER:KEMCO8OSS104KSRA
+Q QUANTITY 2SOO
+CAPACITOR
+ROHS-PRC
+.100UF SOV
+10%
+DATE CODE :2542
+1T LOT :254270641
+C OF O MEXICO
+T
+5":415 (11]
+UAIA
+45239701
+KEMET P/N CO8OSS104KSRAC7800
+KEMET
+MIL P/N
+• YAGTO COMPARY
+A
+Y
+R</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>12ff412711e55208f1087c07c64b8bfc2ab78a93e3bb43463c7d24f2112eeb17</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M313" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-03-14 06:33:53</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>KEMC0805S104KSRA</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>6.66s</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>!
+7
+P PART NUMBER:KEMCO805S104KSRA
+Q QUANTITY 2500
+CAPACITOR
+ROHS-PRC
+.100UF 50V
+10%
+DATE CODE :2S42
+1T LOT :254270641
+C OF O MEXICO
+SPL4IE
+45239701
+KEMET P/N CO8OSS104KSRAC7800
+KEMET
+MIL P/N
+O YAGEO COMPORTY</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>5d1f6dfc5634fe5728183691d2412682bee342086609b31d362484d08ac32de6</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>100000100018320103</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/scans.xlsx
+++ b/data/scans.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N314"/>
+  <dimension ref="A1:N326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23615,14 +23615,952 @@
           <t>CAPACITOR</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>100000100018320103</t>
-        </is>
+      <c r="M314" t="n">
+        <v>1.000001000183201e+17</v>
       </c>
       <c r="N314" t="inlineStr">
         <is>
           <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:01:23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>KEMC0805S104K5RA</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>45739701</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>6.59s</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO805S104K5RA
+4
+CAPACITOR
+ROHS-PRC
+Q QUANTITY2SOO
+.100UF SOV
+10%
+DATE CODE :2542
+C OF O MEXICO
+1T LOT:254270641
+3*,436
+45739701
+KEMET
+KEMET P/N CO8OSS104KSRAC7800
+"
+MIL P/N</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>7b7fedb0f9e8919c51137ebc083cb3029393621d4c907917505a1f8151194260</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M315" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:02:09</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104KSRA</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>45239701</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>5.78s</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO8OSS104KSRA
+CAPACITOR
+ROHS-PRC
+Q QUANTITY 2SOO
+.100UF SOV
+10%
+DATE CODE :2542
+C OF O MEXICO
+1T LOT:254270641
+SPLAIG
+45239701
+KEMET
+KEMET P/N C08OSS104KSRAC7800
+MIL P/N
+O YACEOC
+T0</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>e327dac368053212319a0e136175d464629abbf569d1b2edf45af8e24a8f2cf6</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M316" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:02:25</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>KEMC0805S104KSRA</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>5.75s</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO805S104KSRA
+ROHS-PRC
+CAPACITOR
+Q QUANTITY 2500
+.100UF 50V
+10%
+41
+DATE CODE :2542
+C OF O MEXICO
+1T LOT:254270641
+B
+39L486
+45239701
+KEMET
+KEMET P/N COBOSS104K5RAC7800
+MIL P/N
+A YAGTO CY
+M</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>471a353e5a5a5310ab9e980ea2722618d8d596b8beca8fc2dbb06cd8f1460c24</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M317" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:02:53</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>KEMET</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>KEMCO8OSS104K5RA</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>6.34s</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>P PART NUMBER:KEMCO8OSS104K5RA
+'
+ROHS-PRC
+CAPACITOR
+Q QUANTITY 2500
+10%
+.100UF 50V
+DATE CODE :2S42
+C OF O MEXICO
+1T LOT :254270641
+SPLALG
+45239701
+KEMET
+KEMET P/N CO80SS104K5RAC7800
+MIL P/N
+A YAGEO C
+8</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>45a24afd71e46ec3dbbfafed2980ad41a72195e54ca811b49f5bfaa575a56922</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>254270641</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>CAPACITOR</t>
+        </is>
+      </c>
+      <c r="M318" t="n">
+        <v>1.000001000183201e+17</v>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>185101626</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:03:31</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>5.60s</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>AUCH
+OF
+0
+1P 253468
+(PB)
+Q 1000 ST
+2
+•
+V
+(11) 012685
+ROHS
+O
+√
+RIVVTE
+0 8,0 -JXS53P4 - 10 -20/20 -T1-AEC-LF
+OHEPIUG6-85</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>6afee00b4815b5d2d70d4c9dc56a6685aca5cf2bb3b4e9c2cffb84433ed85ff7</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:04:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>3.20s</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>b48df7f1252fdf31921be71a1cd19248312d356205525a731867efd343e6e22f</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:04:28</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>5.21s</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>JAUCH
+00
+1P 253468
+() 1000 ST
+P
+P.
+V
+_
+ROHS
+O
+1T 012685
+−
+PIMZVTY
+Q 8,0 -JXS53P4 -10 -20/20-T1 - AEC-LF
+OMEPTO126-85
+T0</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>c177e5cf187f15de4f253c637c339f1173b8cef8bbb90ca816f3b8943bf37204</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-03-14 08:30:25</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>8.23s</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>JAUCH
+0
+O
+1P 253468
+7
+(0) 1000 ST
+2
+−
+1T 012685
+ROHS
+A
+POIWNWIY
+Q 8,0 -JXS53P4 - 10-20/20-T1-AEC-LF
+OMEP19136-85</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>9e5eb45d7131df79a2a7e8b8b396b05a487ba8808e29e775048f2c9bb65b40d2</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-03-14 08:30:44</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>7.25s</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>AUCH
+9
+1P 253468
+(0) 1000 ST
+3
+-
+H
+(1) 012685
+ROHS
+YOIUSSVY
+Q 8,0 -JXS53P4 - 10 -20/20 -T1-AEC-LF
+ONEPL016-85</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>3308ba08452294d2db73f83ad4ac6e9f2733cab8b7f607464ba361c1ebbb2d2e</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-03-14 08:30:58</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>6.72s</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>DAUCH
+O.
+O.5
+1P 253468
+() 1000 ST
+−
+0
+:
+(11) 012685
+ROHS
+20113V1Y
+Q 8,0-JXS53P4 -10-20/20-T1-AEC-LF
+OMEPT126-85</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>1e4d723a1a3f70626b53b4e52bb9625a984a5d1a25d1e67cbeb16d40e36b4cbf</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-03-14 08:31:13</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>012685</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>7.34s</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>JAUCH
+0
+1P 253468
+Q 1000 ST
+AB
+:
+2
+J
+D
+1T 012685
+ROHS
+POIVEVTY
+Q 8,0-JXS53P4 -10 -20/20-T1-AEC-LF
+OMEPI0136-85
+CM</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>f7316eefe06a2206d9897438695e9e58272fbd9ef8783464ea36f0da3e9dbc99</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" t="n">
+        <v>1.000001000183289e+17</v>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>185099607</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-03-14 08:34:48</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>JAUCH</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>253468</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>052</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>paddleocr</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>7.38s</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>JAUCH
+052
+1P 253468
+0
+(PB
+HE
+Q 1000 ST
+.
+—
+ROHS
+1T 012685
+−
+YOIRVTY
+Q 8,0 -JXS53P4 -10 -20/20 -T1-AEC-LF
++
+ONEPT9126 -85</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>6f4915783edeca346827540c80c1e1ffb24f238ce0363ed7e508c20964e9317e</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>012685</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>100000100018328942</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>185099607</t>
         </is>
       </c>
     </row>
